--- a/data_extactor/batch_10_fa/trimmed/batch_0014_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0014_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | مدیریت و امور اداری | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | امور اداری | امور حقوقی و دولتی | آموزش و تدریس</t>
+          <t>زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | خدمات مشتری و شخصی | اداری | قانون و دولت | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | متصدیان ورود اطلاعات | مدیران پایگاه داده | متصدیان بایگانی و سوابق | متخصصان فناوری اطلاعات سلامت و ثبت اطلاعات پزشکی | تحلیل‌گران امنیت اطلاعات | متصدیان امور اداری و دفتری</t>
+          <t>مدیران خدمات اداری و پشتیبانی | متصدیان ورود اطلاعات و داده‌آمایی | مدیران پایگاه داده | متصدیان بایگانی و اسناد | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | تحلیل‌گران امنیت اطلاعات | متصدیان امور دفتری و امور عمومی اداری</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | مخابرات و ارتباطات | زبان انگلیسی | ریاضیات | مهندسی و فناوری | ایمنی و امنیت عمومی</t>
+          <t>رایانه و الکترونیک | مخابرات | زبان انگلیسی | ریاضیات | مهندسی و فناوری | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مهندسان معمار شبکه | تحلیل‌گران سامانه‌های رایانه‌ای | تحلیل‌گران جرم‌یابی دیجیتال | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | راهبران شبکه و سامانه‌های رایانه‌ای | توسعه‌دهندگان نرم‌افزار</t>
+          <t>معماران شبکه رایانه‌ای | تحلیل‌گران سیستم‌های کامپیوتری | تحلیل‌گران جرم‌یابی دیجیتال و پاسخ به حوادث | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | نگارش | نظارت | سخن گفتن | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | نظارت | سخن گفتن | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | مهندسی و فناوری | زبان انگلیسی | مخابرات و ارتباطات | خدمات مشتریان و خدمات فردی</t>
+          <t>رایانه و الکترونیک | مهندسی و فناوری | زبان انگلیسی | مخابرات | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | مرتب‌سازی اطلاعات | حساسیت به مسئله | استدلال استقرایی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مهندسان معمار شبکه | تحلیل‌گران سامانه‌های رایانه‌ای | تحلیل‌گران جرم‌یابی دیجیتال | تحلیل‌گران امنیت اطلاعات | راهبران شبکه و سامانه‌های رایانه‌ای | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | توسعه‌دهندگان نرم‌افزار</t>
+          <t>معماران شبکه رایانه‌ای | تحلیل‌گران سیستم‌های کامپیوتری | تحلیل‌گران جرم‌یابی دیجیتال و پاسخ به حوادث | تحلیل‌گران امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | امور حقوقی و دولتی | زبان انگلیسی | مخابرات و ارتباطات | ایمنی و امنیت عمومی | مهندسی و فناوری</t>
+          <t>رایانه و الکترونیک | قانون و دولت | زبان انگلیسی | مخابرات | ایمنی و امنیت عمومی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تحلیل‌گران سامانه‌های رایانه‌ای | کارشناسان آزمایشگاه تشخیص هویت و علوم جنایی | کارشناسان بازرسی، کشف و تحلیل تقلب | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | افسران تشخیص هویت و امور پرونده‌ها در پلیس</t>
+          <t>تحلیل‌گران سیستم‌های کامپیوتری | کاردان‌ها و تکنسین‌های علوم آزمایشگاهی و کشف علمی جرایم | کارشناسان بازرسی، کشف و تحلیل تقلب | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | کارشناسان تشخیص هویت و ثبت سوابق پلیس</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | ریاضیات | زبان انگلیسی | مهندسی و فناوری | مخابرات و ارتباطات | اقتصاد و حسابداری</t>
+          <t>رایانه و الکترونیک | ریاضیات | زبان انگلیسی | مهندسی و فناوری | مخابرات | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>برنامه‌نویسان رایانه | تحلیل‌گران سامانه‌های رایانه‌ای | مهندسان و معماران سامانه‌های رایانه‌ای | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | توسعه‌دهندگان نرم‌افزار | توسعه‌دهندگان وب</t>
+          <t>برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | توسعه‌دهندگان نرم‌افزار | توسعه‌دهندگان وب</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | نظارت | استراتژی‌های یادگیری | علوم پایه | ریاضیات</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | زبان انگلیسی | مخابرات و ارتباطات | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | مدیریت و امور اداری</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | مخابرات | خدمات مشتری و شخصی | مهندسی و فناوری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان معمار شبکه | برنامه‌نویسان رایانه | تحلیل‌گران سامانه‌های رایانه‌ای | مدیران فناوری اطلاعات و سامانه‌های رایانه‌ای | مهندسان امنیت اطلاعات | راهبران شبکه و سامانه‌های رایانه‌ای | توسعه‌دهندگان نرم‌افزار</t>
+          <t>معماران شبکه رایانه‌ای | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نگارش | شنیدن فعال | درک مطلب | سخن گفتن | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | نگارش | گوش دادن فعال | درک مطلب | سخن گفتن | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | رایانه و الکترونیک | مدیریت و امور اداری | مهندسی و فناوری | اقتصاد و حسابداری | مدیریت منابع انسانی و امور پرسنلی</t>
+          <t>زبان انگلیسی | رایانه و الکترونیک | مدیریت و اداره | مهندسی و فناوری | اقتصاد و حسابداری | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | درک شفاهی</t>
+          <t>درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | درک شفاهی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تحلیل‌گران سامانه‌های رایانه‌ای | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران فناوری اطلاعات و سامانه‌های رایانه‌ای | تحلیل‌گران مدیریت | راهبران شبکه و سامانه‌های رایانه‌ای | کارشناسان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار</t>
+          <t>تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | کارشناسان تحلیل مدیریت و روش‌ها | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | ریاضیات | درک مطلب | شنیدن فعال | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
+          <t>تفکر انتقادی | ریاضیات | درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری | زبان انگلیسی | امور حقوقی و دولتی</t>
+          <t>ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری | زبان انگلیسی | قانون و دولت</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | استدلال استقرایی | تسلط بر کار با اعداد | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی</t>
+          <t>استدلال ریاضی | استدلال استقرایی | توانایی عددی | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | تحلیل‌گران اعتباری | اقتصاددانان | تحلیل‌گران محاسبات مالی | کارشناسان ریسک مالی | کارشناسان صدور بیمه‌نامه (ارزیابان ریسک) | آمارشناسان</t>
+          <t>حسابداران و حسابرسان | تحلیل‌گران اعتبارات و تسهیلات | اقتصاددانان | تحلیل‌گران کمّی مالی | کارشناسان ریسک مالی | کارشناسان صدور بیمه‌نامه و ارزیابی ریسک | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ریاضیات | تفکر انتقادی | درک مطلب | یادگیری فعال | علوم پایه | نگارش | شنیدن فعال | استراتژی‌های یادگیری | سخن گفتن | نظارت</t>
+          <t>ریاضیات | تفکر انتقادی | درک مطلب | یادگیری فعال | علوم | نگارش | گوش دادن فعال | راهبردهای یادگیری | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ریاضیات | آموزش و تدریس | رایانه و الکترونیک | زبان انگلیسی | فیزیک</t>
+          <t>ریاضیات | آموزش و پرورش | رایانه و الکترونیک | زبان انگلیسی | فیزیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | تسلط بر کار با اعداد | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | ابتکار و اصالت</t>
+          <t>استدلال ریاضی | توانایی عددی | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | اصالت</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>دانشمندان پژوهش‌های رایانه و اطلاعات | دانشمندان داده | تحلیل‌گران محاسبات مالی | استادان و مدرسان علوم ریاضی در دانشگاه | تحلیل‌گران تحقیق در عملیات | فیزیک‌دانان | آمارشناسان</t>
+          <t>پژوهشگران علوم رایانه و اطلاعات | دانشمندان داده | تحلیل‌گران کمّی مالی | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | تحلیل‌گران تحقیق در عملیات | فیزیک‌دانان | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ریاضیات | نگارش | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | یادگیری فعال | علوم پایه | استراتژی‌های یادگیری</t>
+          <t>ریاضیات | نگارش | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ریاضیات | رایانه و الکترونیک | مهندسی و فناوری | تولید و فراوری | زبان انگلیسی | طراحی | آموزش و تدریس</t>
+          <t>ریاضیات | رایانه و الکترونیک | مهندسی و فناوری | تولید و فرآوری | زبان انگلیسی | طراحی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | تسلط بر کار با اعداد</t>
+          <t>استدلال ریاضی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | توانایی عددی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تحلیل‌گران هوش تجاری | دانشمندان داده | تحلیل‌گران محاسبات مالی | مهندسان صنایع | تحلیل‌گران مدیریت | ریاضی‌دانان | آمارشناسان</t>
+          <t>تحلیل‌گران هوش تجاری | دانشمندان داده | تحلیل‌گران کمّی مالی | مهندسان صنایع | کارشناسان تحلیل مدیریت و روش‌ها | ریاضی‌دانان | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
